--- a/artfynd/A 35944-2024 artfynd.xlsx
+++ b/artfynd/A 35944-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487910</v>
+        <v>120487809</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>80499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436697</v>
+        <v>436699</v>
       </c>
       <c r="R2" t="n">
-        <v>6757740</v>
+        <v>6757724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487710</v>
+        <v>120487795</v>
       </c>
       <c r="B3" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436697</v>
+        <v>436733</v>
       </c>
       <c r="R3" t="n">
-        <v>6757699</v>
+        <v>6757710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487714</v>
+        <v>120487756</v>
       </c>
       <c r="B4" t="n">
-        <v>95478</v>
+        <v>4766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +896,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436645</v>
+        <v>436707</v>
       </c>
       <c r="R4" t="n">
-        <v>6757695</v>
+        <v>6757714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487713</v>
+        <v>120487910</v>
       </c>
       <c r="B5" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436698</v>
+        <v>436697</v>
       </c>
       <c r="R5" t="n">
-        <v>6757702</v>
+        <v>6757740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487712</v>
+        <v>120487794</v>
       </c>
       <c r="B6" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1105,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436695</v>
+        <v>436709</v>
       </c>
       <c r="R6" t="n">
-        <v>6757699</v>
+        <v>6757703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487801</v>
+        <v>120487758</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436713</v>
+        <v>436715</v>
       </c>
       <c r="R7" t="n">
-        <v>6757748</v>
+        <v>6757711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487795</v>
+        <v>120487909</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,43 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436733</v>
+        <v>436714</v>
       </c>
       <c r="R8" t="n">
-        <v>6757710</v>
+        <v>6757748</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487740</v>
+        <v>120487801</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,35 +1523,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1555,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436613</v>
+        <v>436713</v>
       </c>
       <c r="R10" t="n">
-        <v>6757658</v>
+        <v>6757748</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487909</v>
+        <v>120487721</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436714</v>
+        <v>436717</v>
       </c>
       <c r="R11" t="n">
-        <v>6757748</v>
+        <v>6757737</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487794</v>
+        <v>120487712</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,43 +1732,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436709</v>
+        <v>436695</v>
       </c>
       <c r="R12" t="n">
-        <v>6757703</v>
+        <v>6757699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487983</v>
+        <v>120487740</v>
       </c>
       <c r="B13" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,31 +1834,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436692</v>
+        <v>436613</v>
       </c>
       <c r="R13" t="n">
-        <v>6757720</v>
+        <v>6757658</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487715</v>
+        <v>120487832</v>
       </c>
       <c r="B14" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436622</v>
+        <v>436716</v>
       </c>
       <c r="R14" t="n">
-        <v>6757683</v>
+        <v>6757737</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487981</v>
+        <v>120487710</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>95478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,43 +2047,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436744</v>
+        <v>436697</v>
       </c>
       <c r="R15" t="n">
-        <v>6757697</v>
+        <v>6757699</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487772</v>
+        <v>120487715</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,39 +2153,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436619</v>
+        <v>436622</v>
       </c>
       <c r="R16" t="n">
-        <v>6757657</v>
+        <v>6757683</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2239,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487711</v>
+        <v>120487713</v>
       </c>
       <c r="B17" t="n">
         <v>95478</v>
@@ -2289,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436705</v>
+        <v>436698</v>
       </c>
       <c r="R17" t="n">
-        <v>6757711</v>
+        <v>6757702</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487809</v>
+        <v>120487714</v>
       </c>
       <c r="B18" t="n">
-        <v>80499</v>
+        <v>95478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2367,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2391,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436699</v>
+        <v>436645</v>
       </c>
       <c r="R18" t="n">
-        <v>6757724</v>
+        <v>6757695</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487758</v>
+        <v>120487981</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>5169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,38 +2455,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436715</v>
+        <v>436744</v>
       </c>
       <c r="R19" t="n">
-        <v>6757711</v>
+        <v>6757697</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487832</v>
+        <v>120487772</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,34 +2566,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436716</v>
+        <v>436619</v>
       </c>
       <c r="R20" t="n">
-        <v>6757737</v>
+        <v>6757657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487756</v>
+        <v>120487711</v>
       </c>
       <c r="B21" t="n">
-        <v>4766</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,43 +2669,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436707</v>
+        <v>436705</v>
       </c>
       <c r="R21" t="n">
-        <v>6757714</v>
+        <v>6757711</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,10 +2759,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487721</v>
+        <v>120487983</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2780,34 +2775,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436717</v>
+        <v>436692</v>
       </c>
       <c r="R22" t="n">
-        <v>6757737</v>
+        <v>6757720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 35944-2024 artfynd.xlsx
+++ b/artfynd/A 35944-2024 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487982</v>
+        <v>120487721</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,39 +1420,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436697</v>
+        <v>436717</v>
       </c>
       <c r="R9" t="n">
-        <v>6757740</v>
+        <v>6757737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487801</v>
+        <v>120487982</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,27 +1522,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436713</v>
+        <v>436697</v>
       </c>
       <c r="R10" t="n">
-        <v>6757748</v>
+        <v>6757740</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487721</v>
+        <v>120487801</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>8432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436717</v>
+        <v>436713</v>
       </c>
       <c r="R11" t="n">
-        <v>6757737</v>
+        <v>6757748</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487712</v>
+        <v>120487832</v>
       </c>
       <c r="B12" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436695</v>
+        <v>436716</v>
       </c>
       <c r="R12" t="n">
-        <v>6757699</v>
+        <v>6757737</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487740</v>
+        <v>120487712</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,43 +1838,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436613</v>
+        <v>436695</v>
       </c>
       <c r="R13" t="n">
-        <v>6757658</v>
+        <v>6757699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487832</v>
+        <v>120487740</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,34 +1940,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436716</v>
+        <v>436613</v>
       </c>
       <c r="R14" t="n">
-        <v>6757737</v>
+        <v>6757658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 35944-2024 artfynd.xlsx
+++ b/artfynd/A 35944-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487809</v>
+        <v>120487714</v>
       </c>
       <c r="B2" t="n">
-        <v>80499</v>
+        <v>95478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436699</v>
+        <v>436645</v>
       </c>
       <c r="R2" t="n">
-        <v>6757724</v>
+        <v>6757695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487795</v>
+        <v>120487712</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436733</v>
+        <v>436695</v>
       </c>
       <c r="R3" t="n">
-        <v>6757710</v>
+        <v>6757699</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487756</v>
+        <v>120487713</v>
       </c>
       <c r="B4" t="n">
-        <v>4766</v>
+        <v>95478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436707</v>
+        <v>436698</v>
       </c>
       <c r="R4" t="n">
-        <v>6757714</v>
+        <v>6757702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487910</v>
+        <v>120487721</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436697</v>
+        <v>436717</v>
       </c>
       <c r="R5" t="n">
-        <v>6757740</v>
+        <v>6757737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487758</v>
+        <v>120487756</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>4766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1202,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436715</v>
+        <v>436707</v>
       </c>
       <c r="R7" t="n">
-        <v>6757711</v>
+        <v>6757714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487909</v>
+        <v>120487795</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,38 +1309,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436714</v>
+        <v>436733</v>
       </c>
       <c r="R8" t="n">
-        <v>6757748</v>
+        <v>6757710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487721</v>
+        <v>120487981</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,34 +1420,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436717</v>
+        <v>436744</v>
       </c>
       <c r="R9" t="n">
-        <v>6757737</v>
+        <v>6757697</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487982</v>
+        <v>120487740</v>
       </c>
       <c r="B10" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,31 +1523,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1551,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436697</v>
+        <v>436613</v>
       </c>
       <c r="R10" t="n">
-        <v>6757740</v>
+        <v>6757658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487801</v>
+        <v>120487909</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,40 +1634,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436713</v>
+        <v>436714</v>
       </c>
       <c r="R11" t="n">
         <v>6757748</v>
@@ -1720,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487832</v>
+        <v>120487710</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436716</v>
+        <v>436697</v>
       </c>
       <c r="R12" t="n">
-        <v>6757737</v>
+        <v>6757699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487712</v>
+        <v>120487910</v>
       </c>
       <c r="B13" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436695</v>
+        <v>436697</v>
       </c>
       <c r="R13" t="n">
-        <v>6757699</v>
+        <v>6757740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487740</v>
+        <v>120487711</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,43 +1944,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436613</v>
+        <v>436705</v>
       </c>
       <c r="R14" t="n">
-        <v>6757658</v>
+        <v>6757711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487710</v>
+        <v>120487801</v>
       </c>
       <c r="B15" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,38 +2042,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436697</v>
+        <v>436713</v>
       </c>
       <c r="R15" t="n">
-        <v>6757699</v>
+        <v>6757748</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487715</v>
+        <v>120487758</v>
       </c>
       <c r="B16" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436622</v>
+        <v>436715</v>
       </c>
       <c r="R16" t="n">
-        <v>6757683</v>
+        <v>6757711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487713</v>
+        <v>120487983</v>
       </c>
       <c r="B17" t="n">
-        <v>95478</v>
+        <v>5169</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,38 +2251,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436698</v>
+        <v>436692</v>
       </c>
       <c r="R17" t="n">
-        <v>6757702</v>
+        <v>6757720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487714</v>
+        <v>120487982</v>
       </c>
       <c r="B18" t="n">
-        <v>95478</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,38 +2358,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436645</v>
+        <v>436697</v>
       </c>
       <c r="R18" t="n">
-        <v>6757695</v>
+        <v>6757740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,10 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487981</v>
+        <v>120487715</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>95478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,43 +2465,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436744</v>
+        <v>436622</v>
       </c>
       <c r="R19" t="n">
-        <v>6757697</v>
+        <v>6757683</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487772</v>
+        <v>120487809</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>80499</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2566,39 +2571,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436619</v>
+        <v>436699</v>
       </c>
       <c r="R20" t="n">
-        <v>6757657</v>
+        <v>6757724</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487711</v>
+        <v>120487772</v>
       </c>
       <c r="B21" t="n">
-        <v>95478</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,34 +2673,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436705</v>
+        <v>436619</v>
       </c>
       <c r="R21" t="n">
-        <v>6757711</v>
+        <v>6757657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,10 +2764,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487983</v>
+        <v>120487832</v>
       </c>
       <c r="B22" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,43 +2776,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436692</v>
+        <v>436716</v>
       </c>
       <c r="R22" t="n">
-        <v>6757720</v>
+        <v>6757737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 35944-2024 artfynd.xlsx
+++ b/artfynd/A 35944-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487714</v>
+        <v>120487801</v>
       </c>
       <c r="B2" t="n">
-        <v>95478</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436645</v>
+        <v>436713</v>
       </c>
       <c r="R2" t="n">
-        <v>6757695</v>
+        <v>6757748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487712</v>
+        <v>120487721</v>
       </c>
       <c r="B3" t="n">
-        <v>95478</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436695</v>
+        <v>436717</v>
       </c>
       <c r="R3" t="n">
-        <v>6757699</v>
+        <v>6757737</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487713</v>
+        <v>120487710</v>
       </c>
       <c r="B4" t="n">
         <v>95478</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436698</v>
+        <v>436697</v>
       </c>
       <c r="R4" t="n">
-        <v>6757702</v>
+        <v>6757699</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487721</v>
+        <v>120487740</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +998,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436717</v>
+        <v>436613</v>
       </c>
       <c r="R5" t="n">
-        <v>6757737</v>
+        <v>6757658</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487794</v>
+        <v>120487772</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,31 +1109,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436709</v>
+        <v>436619</v>
       </c>
       <c r="R6" t="n">
-        <v>6757703</v>
+        <v>6757657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487756</v>
+        <v>120487981</v>
       </c>
       <c r="B7" t="n">
-        <v>4766</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436707</v>
+        <v>436744</v>
       </c>
       <c r="R7" t="n">
-        <v>6757714</v>
+        <v>6757697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487795</v>
+        <v>120487712</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>95478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,43 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436733</v>
+        <v>436695</v>
       </c>
       <c r="R8" t="n">
-        <v>6757710</v>
+        <v>6757699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1413,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487981</v>
+        <v>120487983</v>
       </c>
       <c r="B9" t="n">
         <v>5169</v>
@@ -1449,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436744</v>
+        <v>436692</v>
       </c>
       <c r="R9" t="n">
-        <v>6757697</v>
+        <v>6757720</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487740</v>
+        <v>120487795</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,35 +1532,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1560,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436613</v>
+        <v>436733</v>
       </c>
       <c r="R10" t="n">
-        <v>6757658</v>
+        <v>6757710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487909</v>
+        <v>120487711</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436714</v>
+        <v>436705</v>
       </c>
       <c r="R11" t="n">
-        <v>6757748</v>
+        <v>6757711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487710</v>
+        <v>120487715</v>
       </c>
       <c r="B12" t="n">
         <v>95478</v>
@@ -1764,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436697</v>
+        <v>436622</v>
       </c>
       <c r="R12" t="n">
-        <v>6757699</v>
+        <v>6757683</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487711</v>
+        <v>120487758</v>
       </c>
       <c r="B14" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,7 +1973,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436705</v>
+        <v>436715</v>
       </c>
       <c r="R14" t="n">
         <v>6757711</v>
@@ -2030,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487801</v>
+        <v>120487982</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,27 +2051,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2075,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436713</v>
+        <v>436697</v>
       </c>
       <c r="R15" t="n">
-        <v>6757748</v>
+        <v>6757740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487758</v>
+        <v>120487809</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>80499</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436715</v>
+        <v>436699</v>
       </c>
       <c r="R16" t="n">
-        <v>6757711</v>
+        <v>6757724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487983</v>
+        <v>120487832</v>
       </c>
       <c r="B17" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,43 +2256,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436692</v>
+        <v>436716</v>
       </c>
       <c r="R17" t="n">
-        <v>6757720</v>
+        <v>6757737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487982</v>
+        <v>120487713</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>95478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,43 +2358,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436697</v>
+        <v>436698</v>
       </c>
       <c r="R18" t="n">
-        <v>6757740</v>
+        <v>6757702</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,10 +2448,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487715</v>
+        <v>120487909</v>
       </c>
       <c r="B19" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,21 +2464,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2493,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436622</v>
+        <v>436714</v>
       </c>
       <c r="R19" t="n">
-        <v>6757683</v>
+        <v>6757748</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487809</v>
+        <v>120487756</v>
       </c>
       <c r="B20" t="n">
-        <v>80499</v>
+        <v>4766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,38 +2562,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436699</v>
+        <v>436707</v>
       </c>
       <c r="R20" t="n">
-        <v>6757724</v>
+        <v>6757714</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487772</v>
+        <v>120487714</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,39 +2673,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436619</v>
+        <v>436645</v>
       </c>
       <c r="R21" t="n">
-        <v>6757657</v>
+        <v>6757695</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,10 +2759,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487832</v>
+        <v>120487794</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,38 +2771,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436716</v>
+        <v>436709</v>
       </c>
       <c r="R22" t="n">
-        <v>6757737</v>
+        <v>6757703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 35944-2024 artfynd.xlsx
+++ b/artfynd/A 35944-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487794</v>
+        <v>120487710</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436709</v>
+        <v>436697</v>
       </c>
       <c r="R2" t="n">
-        <v>6757703</v>
+        <v>6757699</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,12 +775,7 @@
         <v>120487711</v>
       </c>
       <c r="B3" t="n">
-        <v>95592</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487713</v>
+        <v>120487712</v>
       </c>
       <c r="B4" t="n">
-        <v>95592</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436698</v>
+        <v>436695</v>
       </c>
       <c r="R4" t="n">
-        <v>6757702</v>
+        <v>6757699</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,55 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487795</v>
+        <v>120487713</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436733</v>
+        <v>436698</v>
       </c>
       <c r="R5" t="n">
-        <v>6757710</v>
+        <v>6757702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487715</v>
+        <v>120487714</v>
       </c>
       <c r="B6" t="n">
-        <v>95592</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436622</v>
+        <v>436645</v>
       </c>
       <c r="R6" t="n">
-        <v>6757683</v>
+        <v>6757695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487714</v>
+        <v>120487715</v>
       </c>
       <c r="B7" t="n">
-        <v>95592</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436645</v>
+        <v>436622</v>
       </c>
       <c r="R7" t="n">
-        <v>6757695</v>
+        <v>6757683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,55 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487983</v>
+        <v>120487809</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436692</v>
+        <v>436699</v>
       </c>
       <c r="R8" t="n">
-        <v>6757720</v>
+        <v>6757724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487909</v>
+        <v>120487740</v>
       </c>
       <c r="B9" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,34 +1365,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436714</v>
+        <v>436613</v>
       </c>
       <c r="R9" t="n">
-        <v>6757748</v>
+        <v>6757658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,15 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487801</v>
+        <v>120487721</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1471,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436713</v>
+        <v>436717</v>
       </c>
       <c r="R10" t="n">
-        <v>6757748</v>
+        <v>6757737</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,55 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487756</v>
+        <v>120487832</v>
       </c>
       <c r="B11" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436707</v>
+        <v>436716</v>
       </c>
       <c r="R11" t="n">
-        <v>6757714</v>
+        <v>6757737</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,37 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487721</v>
+        <v>120487834</v>
       </c>
       <c r="B12" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436717</v>
+        <v>436594</v>
       </c>
       <c r="R12" t="n">
-        <v>6757737</v>
+        <v>6757688</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,37 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487710</v>
+        <v>120487835</v>
       </c>
       <c r="B13" t="n">
-        <v>95592</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436697</v>
+        <v>436584</v>
       </c>
       <c r="R13" t="n">
-        <v>6757699</v>
+        <v>6757687</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,37 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487758</v>
+        <v>120487909</v>
       </c>
       <c r="B14" t="n">
-        <v>57500</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436715</v>
+        <v>436714</v>
       </c>
       <c r="R14" t="n">
-        <v>6757711</v>
+        <v>6757748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,45 +1945,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487982</v>
+        <v>120487910</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
@@ -2136,16 +2045,11 @@
         <v>120487772</v>
       </c>
       <c r="B16" t="n">
-        <v>57363</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2240,47 +2144,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487740</v>
+        <v>120487756</v>
       </c>
       <c r="B17" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2289,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436613</v>
+        <v>436707</v>
       </c>
       <c r="R17" t="n">
-        <v>6757658</v>
+        <v>6757714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,50 +2246,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487832</v>
+        <v>120487981</v>
       </c>
       <c r="B18" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436716</v>
+        <v>436744</v>
       </c>
       <c r="R18" t="n">
-        <v>6757737</v>
+        <v>6757697</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,50 +2348,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487809</v>
+        <v>120487982</v>
       </c>
       <c r="B19" t="n">
-        <v>80550</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436699</v>
+        <v>436697</v>
       </c>
       <c r="R19" t="n">
-        <v>6757724</v>
+        <v>6757740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,50 +2450,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487910</v>
+        <v>120487983</v>
       </c>
       <c r="B20" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436697</v>
+        <v>436692</v>
       </c>
       <c r="R20" t="n">
-        <v>6757740</v>
+        <v>6757720</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,55 +2552,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487981</v>
+        <v>120487758</v>
       </c>
       <c r="B21" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436744</v>
+        <v>436715</v>
       </c>
       <c r="R21" t="n">
-        <v>6757697</v>
+        <v>6757711</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,50 +2649,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487712</v>
+        <v>120487794</v>
       </c>
       <c r="B22" t="n">
-        <v>95592</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436695</v>
+        <v>436709</v>
       </c>
       <c r="R22" t="n">
-        <v>6757699</v>
+        <v>6757703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,6 +2748,210 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120487795</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hagmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>436733</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6757710</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120487801</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hagmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>436713</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6757748</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35944-2024 artfynd.xlsx
+++ b/artfynd/A 35944-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487713</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487714</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487715</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487809</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487740</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487721</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487832</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487834</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487835</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487909</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487910</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487772</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487756</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2345,6 +2430,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487981</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2447,6 +2537,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487982</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2549,6 +2644,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487983</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2646,6 +2746,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487758</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2748,6 +2853,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487794</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2850,6 +2960,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487795</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2952,8 +3067,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487801</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>